--- a/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
+++ b/Docs/QA-Testing/Test_Case_WhiteBox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KCPM - NAM3\Online-Store\Docs\QA-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\sp3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D96FC7-0EF1-42B7-B357-24AF59565231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97837850-651A-48AF-BBA2-511C1F658DA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{9B43A760-E7C9-4B1A-A514-38BB5ECB6014}"/>
   </bookViews>
   <sheets>
     <sheet name="UNIT-TEST-BVA" sheetId="6" r:id="rId1"/>
@@ -333,12 +333,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -348,18 +363,18 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -677,245 +692,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE6C22E-B1A6-4B4D-867C-4780A0308723}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="49.9" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="19.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="49.95" customHeight="1">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:7" ht="49.9" customHeight="1">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="3" t="s">
         <v>48</v>
       </c>
     </row>
